--- a/output/pdf_financials_xlsx/GR.xlsx
+++ b/output/pdf_financials_xlsx/GR.xlsx
@@ -6004,55 +6004,55 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.514599</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.7174779999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.787982</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.254902</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.197824</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.056002</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.06332400000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.074278</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.231798</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.44596</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.534013</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.967179</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.182096</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.060938</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.806974</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.502394</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.236305</v>
       </c>
     </row>
     <row r="93">
@@ -7574,7 +7574,7 @@
         <v>0.092</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.009974999999999999</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0.001125</v>
@@ -10264,7 +10264,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -13620,7 +13624,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -17733,7 +17741,11 @@
           <t>Share-Based Payment Reserve</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -31504,7 +31516,11 @@
           <t>Share-based payment reserve (Note 8) 787,982</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E229" s="5" t="n">
         <v>0.514599</v>
       </c>
@@ -40304,7 +40320,11 @@
           <t>Shares Issued for Exploration and Evaluation Expenditures</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GR.xlsx
+++ b/output/pdf_financials_xlsx/GR.xlsx
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001315</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.726856</v>
+        <v>-1.728171</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.108428</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.725671</v>
+        <v>-1.726986</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.077116</v>
@@ -2508,49 +2508,49 @@
         <v>1.109889</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.053902</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.013329</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.015032</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.006005</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.00311</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.004161</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.006152</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.006308</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.193572</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.893817</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00048</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001459</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000207</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.002969</v>
       </c>
     </row>
     <row r="35">
@@ -2624,49 +2624,49 @@
         <v>1.109889</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.053902</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.029829</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0033</v>
+        <v>0.018332</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.004125</v>
+        <v>0.01013</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.000855</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.001589</v>
+        <v>0.004699</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.233911</v>
+        <v>0.238072</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.190938</v>
+        <v>0.19709</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.116691</v>
+        <v>0.122999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.179656</v>
+        <v>1.373228</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.120674</v>
+        <v>1.014491</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.023406</v>
+        <v>0.023886</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.003062</v>
+        <v>0.004521</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.003757</v>
+        <v>0.003964</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.004533</v>
+        <v>0.007502</v>
       </c>
     </row>
     <row r="37">
@@ -3320,49 +3320,49 @@
         <v>0.017239</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.166257</v>
+        <v>0.112355</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.223703</v>
+        <v>0.210374</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.128073</v>
+        <v>0.113041</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.062662</v>
+        <v>0.056657</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.109415</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.017343</v>
+        <v>0.014233</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.109829</v>
+        <v>0.105668</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.08153000000000001</v>
+        <v>0.075378</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.141964</v>
+        <v>0.135656</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.377684</v>
+        <v>0.184112</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.323327</v>
+        <v>0.42951</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.08702699999999999</v>
+        <v>0.086547</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.034038</v>
+        <v>0.032579</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.073536</v>
+        <v>0.07332900000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.029631</v>
+        <v>0.026662</v>
       </c>
     </row>
     <row r="49">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -46865,7 +46865,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -48598,7 +48598,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -51138,7 +51138,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -58803,7 +58803,7 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
@@ -61471,7 +61471,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">

--- a/output/pdf_financials_xlsx/GR.xlsx
+++ b/output/pdf_financials_xlsx/GR.xlsx
@@ -1337,7 +1337,7 @@
         <v>-0.638418</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-0.654165</v>
+        <v>-0.648165</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.624123</v>
@@ -1399,7 +1399,7 @@
         <v>-0</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.006</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-0</v>
@@ -2085,7 +2085,7 @@
         <v>-0.638418</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.654165</v>
+        <v>-0.648165</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.624123</v>
@@ -2209,7 +2209,7 @@
         <v>-0.622205</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.651865</v>
+        <v>-0.645865</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.621823</v>
@@ -2363,7 +2363,7 @@
         <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.9256902177686238</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.005</v>
+        <v>0.046393</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.021198</v>
@@ -6529,31 +6529,31 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.022285</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>-0.064633</v>
+        <v>-0.039293</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.059145</v>
+        <v>-0.01517</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>-0.034865</v>
+        <v>-0.060344</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0.080553</v>
+        <v>0.07860399999999999</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>-0.032063</v>
+        <v>0.023012</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>-0.0056</v>
+        <v>0.01979</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.040874</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0.037663</v>
+        <v>0.086811</v>
       </c>
     </row>
     <row r="102">
@@ -6839,31 +6839,31 @@
         <v>0.077986</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.145409</v>
+        <v>-0.167694</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.030847</v>
+        <v>0.056187</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.054359</v>
+        <v>-0.019956</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.256767</v>
+        <v>-0.282246</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.210355</v>
+        <v>-0.212304</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.839402</v>
+        <v>0.894477</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>1.473243</v>
+        <v>1.498633</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.264372</v>
+        <v>0.223498</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.926007</v>
+        <v>0.975155</v>
       </c>
     </row>
     <row r="107">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.000531</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -7161,13 +7161,13 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-1.509806</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009374</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -7379,13 +7379,13 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.007903</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.007125</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -7400,19 +7400,19 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.024798</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.037218</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.099768</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -8631,13 +8631,13 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-1.509806</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009374</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8703,13 +8703,13 @@
         <v>-2.158011</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-4.336799</v>
+        <v>-5.846605</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-2.290301</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.596068</v>
+        <v>-0.605442</v>
       </c>
       <c r="Q135" s="1" t="inlineStr">
         <is>
@@ -32569,7 +32569,11 @@
           <t>GST Recoverable</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -34955,7 +34959,11 @@
           <t>Purchase of Equipment</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -35919,7 +35927,11 @@
           <t>Proceeds from Sale of Marketable Securities</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -39041,7 +39053,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -40619,7 +40635,11 @@
           <t>Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -42936,7 +42956,11 @@
           <t>HST Recoverable</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr"/>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E347" t="inlineStr">
         <is>
           <t>-</t>
@@ -43330,7 +43354,11 @@
           <t>Accretion -</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -54896,7 +54924,11 @@
           <t>Future Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
